--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20261020.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20261020.xlsx
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>PEG US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>大眾服務企業集團公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>32,710</t>
+          <t>50,036</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>FE US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>第一能源公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>77,501</t>
+          <t>32,710</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>PEG US</t>
+          <t>FE US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>大眾服務企業集團公司</t>
+          <t>第一能源公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>50,036</t>
+          <t>77,501</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>43,783</t>
+          <t>25,881</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>25,881</t>
+          <t>43,783</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
